--- a/case-study/metrics_with_rubric.xlsx
+++ b/case-study/metrics_with_rubric.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artur\Desktop\Proyectos Investigación\08_Correcion examenes - SoftwareX\Revision 2\Calculo de metricas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\artur\Desktop\Proyectos Investigación\08_Correcion examenes - SoftwareX\Repositorio GitHub\EvaluAI-Project-main\case-study\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F32EA85-350F-4B1A-A672-362F3BA3BC4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40243681-991D-469D-9882-1984527BDB03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2225" yWindow="5283" windowWidth="26930" windowHeight="14419" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="421" yWindow="693" windowWidth="23543" windowHeight="11099" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Paired data" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,6 @@
     <sheet name="ICC" sheetId="3" r:id="rId3"/>
     <sheet name="Confidence Intervals" sheetId="7" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId5"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="102">
   <si>
     <t>Rubric-guided evaluation: AI vs. Human grading – paired cases</t>
   </si>
@@ -324,6 +321,27 @@
   </si>
   <si>
     <t>Error-metric CIs: t-based intervals across the 13 paired submissions. ICC(2,1) CI: F-distribution-based interval using the existing two-way ANOVA components.</t>
+  </si>
+  <si>
+    <t>SD total (0–6)</t>
+  </si>
+  <si>
+    <t>SD normalized (0–1)</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>Mean SD total (0–6)</t>
+  </si>
+  <si>
+    <t>Mean SD normalized (0–1)</t>
+  </si>
+  <si>
+    <t>Paired submissions (n)</t>
+  </si>
+  <si>
+    <t>SD (STDEV.S) across the three AI total-score runs for each paired submission.</t>
   </si>
 </sst>
 </file>
@@ -335,7 +353,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -378,8 +396,28 @@
       <name val="Carlito"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -398,8 +436,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -407,11 +451,132 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD9D9D9"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFE7E6E6"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD9D9D9"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFE7E6E6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFE7E6E6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD9D9D9"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFE7E6E6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -435,21 +600,48 @@
     <xf numFmtId="166" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="4" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{845AE2CE-733A-48D1-8F4E-FCE3B9434D97}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1014,94 +1206,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="Paired data"/>
-      <sheetName val="Metrics"/>
-      <sheetName val="ICC"/>
-      <sheetName val="Confidence Intervals"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="4">
-          <cell r="A4">
-            <v>1</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5">
-            <v>2</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6">
-            <v>3</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7">
-            <v>4</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8">
-            <v>5</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9">
-            <v>7</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10">
-            <v>8</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11">
-            <v>9</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12">
-            <v>10</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13">
-            <v>11</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14">
-            <v>12</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15">
-            <v>13</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16">
-            <v>14</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ChatGPT">
   <a:themeElements>
@@ -1298,63 +1402,63 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AG18"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="17" width="15" customWidth="1"/>
-    <col min="18" max="18" width="16.4140625" customWidth="1"/>
-    <col min="19" max="19" width="13.6640625" customWidth="1"/>
-    <col min="20" max="20" width="16.58203125" customWidth="1"/>
+    <col min="18" max="18" width="16.375" customWidth="1"/>
+    <col min="19" max="19" width="13.625" customWidth="1"/>
+    <col min="20" max="20" width="16.625" customWidth="1"/>
     <col min="21" max="21" width="15.25" customWidth="1"/>
     <col min="22" max="22" width="14.5" customWidth="1"/>
-    <col min="23" max="23" width="13.9140625" customWidth="1"/>
-    <col min="24" max="24" width="14.33203125" customWidth="1"/>
+    <col min="23" max="23" width="13.875" customWidth="1"/>
+    <col min="24" max="24" width="14.375" customWidth="1"/>
     <col min="25" max="25" width="15.5" customWidth="1"/>
     <col min="26" max="26" width="14.25" customWidth="1"/>
-    <col min="27" max="27" width="12.4140625" customWidth="1"/>
-    <col min="28" max="28" width="13.4140625" customWidth="1"/>
-    <col min="29" max="30" width="12.1640625" customWidth="1"/>
-    <col min="31" max="31" width="12.6640625" customWidth="1"/>
+    <col min="27" max="27" width="12.375" customWidth="1"/>
+    <col min="28" max="28" width="13.375" customWidth="1"/>
+    <col min="29" max="30" width="12.125" customWidth="1"/>
+    <col min="31" max="31" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="18.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-      <c r="O1" s="12"/>
-      <c r="P1" s="12"/>
-      <c r="Q1" s="12"/>
-      <c r="R1" s="12"/>
-      <c r="S1" s="12"/>
-      <c r="T1" s="12"/>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="12"/>
-      <c r="AC1" s="12"/>
-      <c r="AD1" s="12"/>
-      <c r="AE1" s="12"/>
-      <c r="AF1" s="12"/>
-      <c r="AG1" s="12"/>
-    </row>
-    <row r="3" spans="1:33" ht="29.95" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:33" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+      <c r="AB1" s="14"/>
+      <c r="AC1" s="14"/>
+      <c r="AD1" s="14"/>
+      <c r="AE1" s="14"/>
+      <c r="AF1" s="14"/>
+      <c r="AG1" s="14"/>
+    </row>
+    <row r="3" spans="1:33" ht="29.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>1</v>
       </c>
@@ -1455,7 +1559,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>1</v>
       </c>
@@ -1578,7 +1682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>2</v>
       </c>
@@ -1701,7 +1805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>3</v>
       </c>
@@ -1818,7 +1922,7 @@
         <v>0.19166666666666668</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>4</v>
       </c>
@@ -1935,7 +2039,7 @@
         <v>0.26111111111111113</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5</v>
       </c>
@@ -2052,7 +2156,7 @@
         <v>0.60277777777777775</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>7</v>
       </c>
@@ -2169,7 +2273,7 @@
         <v>0.23888888888888893</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>8</v>
       </c>
@@ -2286,7 +2390,7 @@
         <v>0.65833333333333333</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>9</v>
       </c>
@@ -2403,7 +2507,7 @@
         <v>0.40277777777777773</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>10</v>
       </c>
@@ -2520,7 +2624,7 @@
         <v>0.3083333333333334</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>11</v>
       </c>
@@ -2637,7 +2741,7 @@
         <v>0.2722222222222222</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>12</v>
       </c>
@@ -2754,7 +2858,7 @@
         <v>0.50555555555555554</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>13</v>
       </c>
@@ -2871,7 +2975,7 @@
         <v>0.37222222222222223</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>14</v>
       </c>
@@ -2988,26 +3092,26 @@
         <v>0.65555555555555556</v>
       </c>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B18" s="11"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11"/>
-      <c r="F18" s="11"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="11"/>
-      <c r="J18" s="11"/>
-      <c r="K18" s="11"/>
-      <c r="L18" s="11"/>
-      <c r="M18" s="11"/>
-      <c r="N18" s="11"/>
-      <c r="O18" s="11"/>
-      <c r="P18" s="11"/>
-      <c r="Q18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3021,23 +3125,43 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="5" width="14" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="3" width="18" customWidth="1"/>
+    <col min="4" max="4" width="19.625" customWidth="1"/>
+    <col min="5" max="5" width="21.25" customWidth="1"/>
+    <col min="8" max="8" width="18.5" customWidth="1"/>
+    <col min="9" max="9" width="18.625" customWidth="1"/>
+    <col min="11" max="11" width="24.5" customWidth="1"/>
+    <col min="12" max="12" width="13.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:12" ht="19.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="G1" s="23" t="s">
+        <v>101</v>
+      </c>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+    </row>
+    <row r="2" spans="1:12" ht="14.3" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G2" s="15"/>
+      <c r="H2" s="15"/>
+      <c r="I2" s="15"/>
+    </row>
+    <row r="3" spans="1:12" ht="42.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>20</v>
       </c>
@@ -3053,8 +3177,23 @@
       <c r="E3" s="3" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="L3" s="26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
         <v>74</v>
       </c>
@@ -3073,8 +3212,27 @@
         <f>SQRT(D4)</f>
         <v>0.26034165586355507</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G4" s="16">
+        <f>'Paired data'!A4</f>
+        <v>1</v>
+      </c>
+      <c r="H4" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V4:X4)</f>
+        <v>1.3597399555105182E-16</v>
+      </c>
+      <c r="I4" s="18">
+        <f t="shared" ref="I4:I16" si="0">H4/6</f>
+        <v>2.2662332591841969E-17</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="L4" s="18">
+        <f>AVERAGE(H4:H16)</f>
+        <v>9.7450191491369811E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="15.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>73</v>
       </c>
@@ -3093,8 +3251,27 @@
         <f>SQRT(D5)</f>
         <v>1.1122760986635105</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G5" s="16">
+        <f>'Paired data'!A5</f>
+        <v>2</v>
+      </c>
+      <c r="H5" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V5:X5)</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="L5" s="28">
+        <f>AVERAGE(I4:I16)</f>
+        <v>1.6241698581894972E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>74</v>
       </c>
@@ -3113,8 +3290,27 @@
         <f>E4/3</f>
         <v>8.6780551954518351E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G6" s="16">
+        <f>'Paired data'!A6</f>
+        <v>3</v>
+      </c>
+      <c r="H6" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V6:X6)</f>
+        <v>0.22912878474779103</v>
+      </c>
+      <c r="I6" s="18">
+        <f t="shared" si="0"/>
+        <v>3.8188130791298507E-2</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>100</v>
+      </c>
+      <c r="L6" s="21">
+        <f>COUNT(G4:G16)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="6" t="s">
         <v>73</v>
       </c>
@@ -3133,22 +3329,72 @@
         <f>E5/3</f>
         <v>0.37075869955450352</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="11"/>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G7" s="16">
+        <f>'Paired data'!A7</f>
+        <v>4</v>
+      </c>
+      <c r="H7" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V7:X7)</f>
+        <v>5.773502691896263E-2</v>
+      </c>
+      <c r="I7" s="18">
+        <f t="shared" si="0"/>
+        <v>9.6225044864937711E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G8" s="16">
+        <f>'Paired data'!A8</f>
+        <v>5</v>
+      </c>
+      <c r="H8" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V8:X8)</f>
+        <v>7.6376261582597499E-2</v>
+      </c>
+      <c r="I8" s="18">
+        <f t="shared" si="0"/>
+        <v>1.2729376930432917E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="G9" s="16">
+        <f>'Paired data'!A9</f>
+        <v>7</v>
+      </c>
+      <c r="H9" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V9:X9)</f>
+        <v>0.28867513459481237</v>
+      </c>
+      <c r="I9" s="18">
+        <f t="shared" si="0"/>
+        <v>4.8112522432468725E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="12"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="G10" s="16">
+        <f>'Paired data'!A10</f>
+        <v>8</v>
+      </c>
+      <c r="H10" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V10:X10)</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="I10" s="18">
+        <f t="shared" si="0"/>
+        <v>8.3333333333333402E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -3167,8 +3413,20 @@
         <f>SQRT(D11)</f>
         <v>1.1068454443176958</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="G11" s="16">
+        <f>'Paired data'!A11</f>
+        <v>9</v>
+      </c>
+      <c r="H11" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V11:X11)</f>
+        <v>0.12583057392117916</v>
+      </c>
+      <c r="I11" s="18">
+        <f t="shared" si="0"/>
+        <v>2.0971762320196527E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>71</v>
       </c>
@@ -3187,11 +3445,81 @@
         <f>E11/6</f>
         <v>0.18447424071961596</v>
       </c>
+      <c r="G12" s="16">
+        <f>'Paired data'!A12</f>
+        <v>10</v>
+      </c>
+      <c r="H12" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V12:X12)</f>
+        <v>2.7194799110210365E-16</v>
+      </c>
+      <c r="I12" s="18">
+        <f t="shared" si="0"/>
+        <v>4.5324665183683939E-17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G13" s="16">
+        <f>'Paired data'!A13</f>
+        <v>11</v>
+      </c>
+      <c r="H13" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V13:X13)</f>
+        <v>0.2081665999466146</v>
+      </c>
+      <c r="I13" s="18">
+        <f t="shared" si="0"/>
+        <v>3.4694433324435767E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G14" s="16">
+        <f>'Paired data'!A14</f>
+        <v>12</v>
+      </c>
+      <c r="H14" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V14:X14)</f>
+        <v>5.7735026918962373E-2</v>
+      </c>
+      <c r="I14" s="18">
+        <f t="shared" si="0"/>
+        <v>9.6225044864937295E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G15" s="16">
+        <f>'Paired data'!A15</f>
+        <v>13</v>
+      </c>
+      <c r="H15" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V15:X15)</f>
+        <v>5.7735026918962373E-2</v>
+      </c>
+      <c r="I15" s="18">
+        <f t="shared" si="0"/>
+        <v>9.6225044864937295E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="G16" s="16">
+        <f>'Paired data'!A16</f>
+        <v>14</v>
+      </c>
+      <c r="H16" s="17">
+        <f>_xlfn.STDEV.S('Paired data'!V16:X16)</f>
+        <v>0.11547005383792526</v>
+      </c>
+      <c r="I16" s="22">
+        <f t="shared" si="0"/>
+        <v>1.9245008972987542E-2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A9:E10"/>
+    <mergeCell ref="G2:I2"/>
+    <mergeCell ref="G1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3200,7 +3528,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:N21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="12" width="14" customWidth="1"/>
@@ -3208,43 +3536,43 @@
     <col min="14" max="14" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="18.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:14" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="12"/>
-      <c r="J1" s="12"/>
-      <c r="K1" s="12"/>
-      <c r="L1" s="12"/>
-      <c r="M1" s="12"/>
-      <c r="N1" s="12"/>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="11"/>
-      <c r="N2" s="11"/>
-    </row>
-    <row r="4" spans="1:14" ht="29" x14ac:dyDescent="0.35">
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+      <c r="M2" s="12"/>
+      <c r="N2" s="12"/>
+    </row>
+    <row r="4" spans="1:14" ht="28.55" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
@@ -3288,7 +3616,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <f>'Paired data'!A4</f>
         <v>1</v>
@@ -3344,7 +3672,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <f>'Paired data'!A5</f>
         <v>2</v>
@@ -3400,7 +3728,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <f>'Paired data'!A6</f>
         <v>3</v>
@@ -3457,7 +3785,7 @@
         <v>3.5769444444444436</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <f>'Paired data'!A7</f>
         <v>4</v>
@@ -3514,7 +3842,7 @@
         <v>1.3910256410256313E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <f>'Paired data'!A8</f>
         <v>5</v>
@@ -3571,7 +3899,7 @@
         <v>1.7729700854700856E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <f>'Paired data'!A9</f>
         <v>7</v>
@@ -3628,7 +3956,7 @@
         <v>0.9855164426537214</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <f>'Paired data'!A10</f>
         <v>8</v>
@@ -3684,7 +4012,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <f>'Paired data'!A11</f>
         <v>9</v>
@@ -3734,7 +4062,7 @@
         <v>4.000000000000007E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <f>'Paired data'!A12</f>
         <v>10</v>
@@ -3784,7 +4112,7 @@
         <v>0.13444444444444398</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <f>'Paired data'!A13</f>
         <v>11</v>
@@ -3834,7 +4162,7 @@
         <v>0.34027777777777768</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <f>'Paired data'!A14</f>
         <v>12</v>
@@ -3884,7 +4212,7 @@
         <v>0.66694444444444478</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <f>'Paired data'!A15</f>
         <v>13</v>
@@ -3934,7 +4262,7 @@
         <v>2.7777777777779063E-4</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17">
         <f>'Paired data'!A16</f>
         <v>14</v>
@@ -3984,7 +4312,7 @@
         <v>2.9469444444444464</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>50</v>
       </c>
@@ -4001,7 +4329,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B21">
         <f>AVERAGE(B5:B17)</f>
         <v>2.203846153846154</v>
@@ -4031,7 +4359,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08CB590-301D-48E0-B838-EDD6A21468A8}">
   <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="22" customWidth="1"/>
@@ -4043,34 +4371,34 @@
     <col min="11" max="11" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="18.25" x14ac:dyDescent="0.35">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:11" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-    </row>
-    <row r="3" spans="1:11" ht="26.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="13" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+    </row>
+    <row r="3" spans="1:11" ht="26.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="11"/>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="B3" s="12"/>
+      <c r="C3" s="12"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="G3" s="12"/>
+      <c r="H3" s="12"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>1</v>
       </c>
@@ -4099,9 +4427,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
-        <f>'[1]Paired data'!A4</f>
+        <f>'Paired data'!A4</f>
         <v>1</v>
       </c>
       <c r="B6" s="8">
@@ -4120,11 +4448,11 @@
         <v>0.13183760683760681</v>
       </c>
       <c r="G6" s="2">
-        <f>MAX(0,F6-K9*_xlfn.SINGLE(_xlfn.STDEV.S(B6:B18))/SQRT(K6))</f>
+        <f>MAX(0,F6-K9*_xlfn.STDEV.S(B6:B18)/SQRT(K6))</f>
         <v>5.0679653852927803E-2</v>
       </c>
       <c r="H6" s="2">
-        <f>F6+K9*_xlfn.SINGLE(_xlfn.STDEV.S(B6:B18))/SQRT(K6)</f>
+        <f>F6+K9*_xlfn.STDEV.S(B6:B18)/SQRT(K6)</f>
         <v>0.21299555982228582</v>
       </c>
       <c r="J6" t="s">
@@ -4135,9 +4463,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
-        <f>'[1]Paired data'!A5</f>
+        <f>'Paired data'!A5</f>
         <v>2</v>
       </c>
       <c r="B7" s="8">
@@ -4156,11 +4484,11 @@
         <v>3.403074548907882E-2</v>
       </c>
       <c r="G7" s="2">
-        <f>MAX(0,F7-K9*_xlfn.SINGLE(_xlfn.STDEV.S(C6:C18))/SQRT(K6))</f>
+        <f>MAX(0,F7-K9*_xlfn.STDEV.S(C6:C18)/SQRT(K6))</f>
         <v>5.4193006215694818E-3</v>
       </c>
       <c r="H7" s="2">
-        <f>F7+K9*_xlfn.SINGLE(_xlfn.STDEV.S(C6:C18))/SQRT(K6)</f>
+        <f>F7+K9*_xlfn.STDEV.S(C6:C18)/SQRT(K6)</f>
         <v>6.2642190356588162E-2</v>
       </c>
       <c r="J7" t="s">
@@ -4171,9 +4499,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
-        <f>'[1]Paired data'!A6</f>
+        <f>'Paired data'!A6</f>
         <v>3</v>
       </c>
       <c r="B8" s="8">
@@ -4206,9 +4534,9 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
-        <f>'[1]Paired data'!A7</f>
+        <f>'Paired data'!A7</f>
         <v>4</v>
       </c>
       <c r="B9" s="8">
@@ -4226,9 +4554,9 @@
         <v>2.1788128296672284</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
-        <f>'[1]Paired data'!A8</f>
+        <f>'Paired data'!A8</f>
         <v>5</v>
       </c>
       <c r="B10" s="8">
@@ -4241,9 +4569,9 @@
       </c>
       <c r="K10" s="8"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
-        <f>'[1]Paired data'!A9</f>
+        <f>'Paired data'!A9</f>
         <v>7</v>
       </c>
       <c r="B11" s="8">
@@ -4273,9 +4601,9 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
-        <f>'[1]Paired data'!A10</f>
+        <f>'Paired data'!A10</f>
         <v>8</v>
       </c>
       <c r="B12" s="8">
@@ -4309,9 +4637,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
-        <f>'[1]Paired data'!A11</f>
+        <f>'Paired data'!A11</f>
         <v>9</v>
       </c>
       <c r="B13" s="8">
@@ -4330,9 +4658,9 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
-        <f>'[1]Paired data'!A12</f>
+        <f>'Paired data'!A12</f>
         <v>10</v>
       </c>
       <c r="B14" s="8">
@@ -4351,9 +4679,9 @@
         <v>3.5769444444444436</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
-        <f>'[1]Paired data'!A13</f>
+        <f>'Paired data'!A13</f>
         <v>11</v>
       </c>
       <c r="B15" s="8">
@@ -4372,9 +4700,9 @@
         <v>1.3910256410256313E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
-        <f>'[1]Paired data'!A14</f>
+        <f>'Paired data'!A14</f>
         <v>12</v>
       </c>
       <c r="B16" s="8">
@@ -4393,9 +4721,9 @@
         <v>1.7729700854700856E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
-        <f>'[1]Paired data'!A15</f>
+        <f>'Paired data'!A15</f>
         <v>13</v>
       </c>
       <c r="B17" s="8">
@@ -4414,9 +4742,9 @@
         <v>0.78457366676709295</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18">
-        <f>'[1]Paired data'!A16</f>
+        <f>'Paired data'!A16</f>
         <v>14</v>
       </c>
       <c r="B18" s="8">
@@ -4435,7 +4763,7 @@
         <v>25.908237212426101</v>
       </c>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J19" t="s">
         <v>90</v>
       </c>
@@ -4444,7 +4772,7 @@
         <v>2.5148903486239518</v>
       </c>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="J20" t="s">
         <v>91</v>
       </c>
@@ -4453,17 +4781,17 @@
         <v>3.0077380459595253</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="33.700000000000003" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="11" t="s">
+    <row r="21" spans="1:11" ht="33.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="11"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
       <c r="J21" t="s">
         <v>48</v>
       </c>
